--- a/BHYT_Auto/data/results/bhyt_20261014_235059_6a50abfc.xlsx
+++ b/BHYT_Auto/data/results/bhyt_20261014_235059_6a50abfc.xlsx
@@ -10,7 +10,7 @@
     <sheet name="BHYT" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BHYT'!$A$1:$P$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BHYT'!$A$1:$P$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2720,8 +2720,1402 @@
       </c>
       <c r="P31" s="4" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>015087008709</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>DT2151520796969</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Hoàng Anh</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>**/**/1987</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Tỉnh Lào Cai</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>15419</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026 - 31/12/2026</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Yên Bái</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Còn giá trị sử dụng</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:58:12+07:00</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>072097012589</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>DN4807216029690</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Tạ Tuấn Vũ</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>**/**/1997</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Tỉnh Tây Ninh</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>72003</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>01/01/2026 - 31/12/2026</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Long An</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Còn giá trị sử dụng</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:58:14+07:00</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>001094015074</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>GD4010125884248</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Nguyễn Tiến Dũng</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>**/**/1994</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>01830</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>16/12/2025 - 15/12/2026</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Còn giá trị sử dụng</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:58:16+07:00</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>093184009969</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>GD4939321719728</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Kiều Oanh</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>**/**/1984</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Tỉnh Hậu Giang</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>93016</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>28/12/2024 - 27/03/2025</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>Hậu Giang</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>Hết hạn</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:58:18+07:00</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>086068009431</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>GD4868616019694</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Phan Ngọc Thanh</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>**/**/1968</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Tỉnh Vĩnh Long</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>86007</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>25/10/2025 - 25/12/2025</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>Vĩnh Long</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>Hết hạn</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:58:20+07:00</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>080186007938</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>GD4808022962210</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Hồ Thị Mỹ Trinh</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>**/**/1986</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Tỉnh Long An</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>80010</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>01/12/2023 - 30/11/2024</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>Long An</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>Hết hạn</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:59:22+07:00</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>046182012441</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>DN4460407002141</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Lê Ái Nhi</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>**/**/1982</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>46114</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>01/01/2026 - 31/12/2026</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Thừa Thiên Huế</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Còn giá trị sử dụng</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:59:24+07:00</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>002086005600</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>DN4310220036897</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Nguyễn Anh Tuấn</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>**/**/1986</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Tỉnh Tuyên Quang</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>31313</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>01/08/2026 - 31/12/2026</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Hải Phòng</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Còn giá trị sử dụng</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:59:30+07:00</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>001079001293</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>GD4010122231674</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Nguyễn Việt Hùng</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>**/**/1979</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Thành phố Hà Nội</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>01070</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>03/05/2024 - 02/05/2025</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>Hết hạn</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:59:32+07:00</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>074081002039</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>DN4797412159846</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Công</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>**/**/1981</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>74147</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>01/05/2026 - 31/12/2026</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Còn giá trị sử dụng</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14T23:59:34+07:00</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>058180006527</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>NGUYỄN THỊ BÍCH THẢO</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>15/04/1980</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
+      <c r="K42" s="3" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr"/>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Lỗi</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:00:59+07:00</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>Hệ thống BHXH</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Không vượt được CAPTCHA sau 6 lần thử</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>027172002282</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>PHẠM THỊ HOA</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>28/08/1972</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Lỗi</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:02:46+07:00</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>Hệ thống BHXH</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>Không vượt được CAPTCHA sau 6 lần thử</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>033176005452</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>GD4010130807804</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Hồng</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>**/**/1976</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>01095</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>23/07/2026 - 22/07/2027</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Hà Nội</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Còn giá trị sử dụng</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:03:35+07:00</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>015096005098</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>DT2151520638084</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Lò Văn Thoáng</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>**/**/1996</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>15901</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>01/02/2026 - 31/12/2026</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Yên Bái</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Còn giá trị sử dụng</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:03:39+07:00</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>094088006823</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>AK2929423015069</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Nguyễn Rung Rinh</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>**/**/1988</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Thành phố Cần Thơ</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>94070</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>01/01/2026 - 31/12/2026</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Còn giá trị sử dụng</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:03:41+07:00</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>046182012441</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>DN4460407002141</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Lê Ái Nhi</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>**/**/1982</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>46114</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>01/01/2026 - 31/12/2026</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Thừa Thiên Huế</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Còn giá trị sử dụng</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:03:44+07:00</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>086190006524</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>GD4898616019158</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Trần Thị Thủy Tiên</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>**/**/1990</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Nữ</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Tỉnh An Giang</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>89009</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>09/05/2024 - 08/05/2025</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>An Giang</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>Hết hạn</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:03:46+07:00</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>006091005867</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>AK2190620269402</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Cao Văn Hải</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>**/**/1991</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>06007</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>20/05/2026 - 31/12/2026</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Thái Nguyên</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Còn giá trị sử dụng</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:04:35+07:00</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>031067016592</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>GD4313122444505</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Phạm Hồng An</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>**/**/1967</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>31002</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>16/09/2023 - 15/09/2024</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>Hải Phòng</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>Mã thẻ 15 ký tự / bảng mã lịch sử</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>Hết hạn</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:04:37+07:00</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>Thông báo BHXH</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P31"/>
+  <autoFilter ref="A1:P50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>